--- a/Lisa Project/Lisa's project.xlsx
+++ b/Lisa Project/Lisa's project.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\C語言\C-Learning\Lisa Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C88BEE64-ABD6-454C-8DE8-6C96E58857CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF9DE544-B4E1-4434-BA13-743ABF99F1E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{DA1E983E-EF55-4F84-98AC-5E562C614A6E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{DA1E983E-EF55-4F84-98AC-5E562C614A6E}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
     <sheet name="工作表2" sheetId="2" r:id="rId2"/>
+    <sheet name="工作表3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1307" uniqueCount="84">
   <si>
     <t>A</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -249,15 +250,88 @@
   </si>
   <si>
     <t>Ken6</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Week</t>
+  </si>
+  <si>
+    <t>=====</t>
+  </si>
+  <si>
+    <t>=======</t>
+  </si>
+  <si>
+    <t>========</t>
+  </si>
+  <si>
+    <t>============</t>
+  </si>
+  <si>
+    <t>==========</t>
+  </si>
+  <si>
+    <t>==============================</t>
+  </si>
+  <si>
+    <t>DM     Brine       HCl</t>
+  </si>
+  <si>
+    <t>小豬</t>
+  </si>
+  <si>
+    <t>小新</t>
+  </si>
+  <si>
+    <t>廣志</t>
+  </si>
+  <si>
+    <t>小豬/屹耳</t>
+  </si>
+  <si>
+    <t>小葵</t>
+  </si>
+  <si>
+    <t>小白</t>
+  </si>
+  <si>
+    <t>屹耳</t>
+  </si>
+  <si>
+    <t>風間</t>
+  </si>
+  <si>
+    <t>阿呆</t>
+  </si>
+  <si>
+    <t>羅賓</t>
+  </si>
+  <si>
+    <t>妮妮</t>
+  </si>
+  <si>
+    <t>正男</t>
+  </si>
+  <si>
+    <t>維尼</t>
+  </si>
+  <si>
+    <t>風間/小新</t>
+  </si>
+  <si>
+    <t>廣志/小白</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="176" formatCode="mm/dd"/>
     <numFmt numFmtId="177" formatCode="m&quot;月&quot;d&quot;日&quot;"/>
+    <numFmt numFmtId="178" formatCode="0.0"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -337,7 +411,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -391,6 +465,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -805,25 +885,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{201778D1-075F-4051-8320-17672C409E34}">
   <dimension ref="C5:AA61"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="4" width="9.08203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.4140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.4140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.4140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.4140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.0703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="9" customWidth="1"/>
-    <col min="15" max="15" width="13.4140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.08203125" customWidth="1"/>
-    <col min="22" max="22" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.35546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.0703125" customWidth="1"/>
+    <col min="22" max="22" width="15.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="4:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="4:27" x14ac:dyDescent="0.35">
       <c r="D5" s="17" t="s">
         <v>6</v>
       </c>
@@ -854,7 +934,7 @@
       <c r="S5" s="17"/>
       <c r="T5" s="17"/>
     </row>
-    <row r="6" spans="4:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="4:27" x14ac:dyDescent="0.35">
       <c r="F6" s="1" t="s">
         <v>12</v>
       </c>
@@ -904,7 +984,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="4:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="4:27" x14ac:dyDescent="0.35">
       <c r="D7" s="2">
         <v>46235</v>
       </c>
@@ -954,7 +1034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="4:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="4:27" x14ac:dyDescent="0.35">
       <c r="D8" s="2">
         <v>46236</v>
       </c>
@@ -1001,7 +1081,7 @@
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
     </row>
-    <row r="9" spans="4:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="4:27" x14ac:dyDescent="0.35">
       <c r="D9" s="2">
         <v>46237</v>
       </c>
@@ -1048,7 +1128,7 @@
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
     </row>
-    <row r="10" spans="4:27" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="4:27" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="D10" s="9">
         <v>46238</v>
       </c>
@@ -1095,7 +1175,7 @@
       <c r="S10" s="11"/>
       <c r="T10" s="11"/>
     </row>
-    <row r="11" spans="4:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="4:27" x14ac:dyDescent="0.35">
       <c r="D11" s="2">
         <v>46239</v>
       </c>
@@ -1142,7 +1222,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="4:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="4:27" x14ac:dyDescent="0.35">
       <c r="D12" s="2">
         <v>46240</v>
       </c>
@@ -1189,7 +1269,7 @@
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
     </row>
-    <row r="13" spans="4:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="4:27" x14ac:dyDescent="0.35">
       <c r="D13" s="2">
         <v>46241</v>
       </c>
@@ -1236,7 +1316,7 @@
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
     </row>
-    <row r="14" spans="4:27" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="4:27" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="D14" s="5">
         <v>46242</v>
       </c>
@@ -1283,7 +1363,7 @@
       <c r="S14" s="7"/>
       <c r="T14" s="7"/>
     </row>
-    <row r="15" spans="4:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="4:27" x14ac:dyDescent="0.35">
       <c r="D15" s="2">
         <v>46243</v>
       </c>
@@ -1330,7 +1410,7 @@
       <c r="Z15" s="1"/>
       <c r="AA15" s="1"/>
     </row>
-    <row r="16" spans="4:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="4:27" x14ac:dyDescent="0.35">
       <c r="D16" s="2">
         <v>46244</v>
       </c>
@@ -1377,7 +1457,7 @@
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
     </row>
-    <row r="17" spans="4:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="4:20" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="D17" s="5">
         <v>46245</v>
       </c>
@@ -1424,7 +1504,7 @@
       <c r="S17" s="7"/>
       <c r="T17" s="7"/>
     </row>
-    <row r="18" spans="4:20" x14ac:dyDescent="0.3">
+    <row r="18" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D18" s="2">
         <v>46246</v>
       </c>
@@ -1471,7 +1551,7 @@
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
     </row>
-    <row r="19" spans="4:20" x14ac:dyDescent="0.3">
+    <row r="19" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D19" s="2">
         <v>46247</v>
       </c>
@@ -1518,7 +1598,7 @@
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
     </row>
-    <row r="20" spans="4:20" x14ac:dyDescent="0.3">
+    <row r="20" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D20" s="2">
         <v>46248</v>
       </c>
@@ -1565,7 +1645,7 @@
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
     </row>
-    <row r="21" spans="4:20" x14ac:dyDescent="0.3">
+    <row r="21" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D21" s="2">
         <v>46249</v>
       </c>
@@ -1612,7 +1692,7 @@
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
     </row>
-    <row r="22" spans="4:20" x14ac:dyDescent="0.3">
+    <row r="22" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D22" s="2">
         <v>46250</v>
       </c>
@@ -1659,7 +1739,7 @@
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
     </row>
-    <row r="23" spans="4:20" x14ac:dyDescent="0.3">
+    <row r="23" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D23" s="2">
         <v>46251</v>
       </c>
@@ -1706,7 +1786,7 @@
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
     </row>
-    <row r="24" spans="4:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="4:20" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="D24" s="5">
         <v>46252</v>
       </c>
@@ -1755,7 +1835,7 @@
       </c>
       <c r="T24" s="7"/>
     </row>
-    <row r="25" spans="4:20" x14ac:dyDescent="0.3">
+    <row r="25" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D25" s="2">
         <v>46253</v>
       </c>
@@ -1802,7 +1882,7 @@
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
     </row>
-    <row r="26" spans="4:20" x14ac:dyDescent="0.3">
+    <row r="26" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D26" s="2">
         <v>46254</v>
       </c>
@@ -1849,7 +1929,7 @@
       <c r="S26" s="1"/>
       <c r="T26" s="1"/>
     </row>
-    <row r="27" spans="4:20" x14ac:dyDescent="0.3">
+    <row r="27" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D27" s="2">
         <v>46255</v>
       </c>
@@ -1896,7 +1976,7 @@
       <c r="S27" s="1"/>
       <c r="T27" s="1"/>
     </row>
-    <row r="28" spans="4:20" x14ac:dyDescent="0.3">
+    <row r="28" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D28" s="2">
         <v>46256</v>
       </c>
@@ -1943,7 +2023,7 @@
       <c r="S28" s="1"/>
       <c r="T28" s="1"/>
     </row>
-    <row r="29" spans="4:20" x14ac:dyDescent="0.3">
+    <row r="29" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D29" s="2">
         <v>46257</v>
       </c>
@@ -1990,7 +2070,7 @@
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
     </row>
-    <row r="30" spans="4:20" x14ac:dyDescent="0.3">
+    <row r="30" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D30" s="2">
         <v>46258</v>
       </c>
@@ -2037,7 +2117,7 @@
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
     </row>
-    <row r="31" spans="4:20" x14ac:dyDescent="0.3">
+    <row r="31" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D31" s="2">
         <v>46259</v>
       </c>
@@ -2084,7 +2164,7 @@
       <c r="S31" s="1"/>
       <c r="T31" s="1"/>
     </row>
-    <row r="32" spans="4:20" x14ac:dyDescent="0.3">
+    <row r="32" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D32" s="2">
         <v>46260</v>
       </c>
@@ -2131,7 +2211,7 @@
       <c r="S32" s="1"/>
       <c r="T32" s="1"/>
     </row>
-    <row r="33" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:20" x14ac:dyDescent="0.35">
       <c r="D33" s="2">
         <v>46261</v>
       </c>
@@ -2178,7 +2258,7 @@
       <c r="S33" s="1"/>
       <c r="T33" s="1"/>
     </row>
-    <row r="34" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:20" x14ac:dyDescent="0.35">
       <c r="D34" s="2">
         <v>46262</v>
       </c>
@@ -2225,7 +2305,7 @@
       <c r="S34" s="1"/>
       <c r="T34" s="1"/>
     </row>
-    <row r="35" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:20" x14ac:dyDescent="0.35">
       <c r="D35" s="2">
         <v>46263</v>
       </c>
@@ -2272,7 +2352,7 @@
       <c r="S35" s="1"/>
       <c r="T35" s="1"/>
     </row>
-    <row r="36" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:20" x14ac:dyDescent="0.35">
       <c r="D36" s="2">
         <v>46264</v>
       </c>
@@ -2319,7 +2399,7 @@
       <c r="S36" s="1"/>
       <c r="T36" s="1"/>
     </row>
-    <row r="37" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:20" x14ac:dyDescent="0.35">
       <c r="D37" s="2">
         <v>46265</v>
       </c>
@@ -2366,7 +2446,7 @@
       <c r="S37" s="1"/>
       <c r="T37" s="1"/>
     </row>
-    <row r="43" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:20" x14ac:dyDescent="0.35">
       <c r="I43">
         <v>1</v>
       </c>
@@ -2386,7 +2466,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C44">
         <v>0</v>
       </c>
@@ -2420,7 +2500,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C45">
         <f>MOD((C44+1),4)</f>
         <v>1</v>
@@ -2462,7 +2542,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C46">
         <f>MOD((C44+2),4)</f>
         <v>2</v>
@@ -2480,7 +2560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C47">
         <f>MOD((C44+3),4)</f>
         <v>3</v>
@@ -2501,7 +2581,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:20" x14ac:dyDescent="0.35">
       <c r="I48">
         <v>3</v>
       </c>
@@ -2513,7 +2593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C49">
         <v>1</v>
       </c>
@@ -2537,7 +2617,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C50">
         <v>2</v>
       </c>
@@ -2551,7 +2631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C51">
         <v>3</v>
       </c>
@@ -2565,7 +2645,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C53">
         <v>0</v>
       </c>
@@ -2579,7 +2659,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C54">
         <f>MOD(C53+2,7)</f>
         <v>2</v>
@@ -2597,7 +2677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C55">
         <f>MOD(C53+4,7)</f>
         <v>4</v>
@@ -2615,7 +2695,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C56">
         <f>MOD(C53+6,7)</f>
         <v>6</v>
@@ -2633,7 +2713,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C59">
         <v>2</v>
       </c>
@@ -2647,7 +2727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C60">
         <v>4</v>
       </c>
@@ -2661,7 +2741,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C61">
         <v>6</v>
       </c>
@@ -2693,14 +2773,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC5B9C8A-20B7-4BD8-AC90-189B0DB1623A}">
   <dimension ref="B2:R55"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="14" width="8.6640625" style="4"/>
-    <col min="15" max="15" width="7.1640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.6640625" style="4"/>
+    <col min="1" max="14" width="8.640625" style="4"/>
+    <col min="15" max="15" width="7.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:18" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="4" t="s">
         <v>31</v>
       </c>
@@ -2733,7 +2813,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:18" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B3" s="14"/>
       <c r="C3" s="14"/>
       <c r="D3" s="14" t="s">
@@ -2782,7 +2862,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B4" s="2">
         <v>46235</v>
       </c>
@@ -2826,7 +2906,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B5" s="2">
         <v>46236</v>
       </c>
@@ -2870,7 +2950,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B6" s="2">
         <v>46237</v>
       </c>
@@ -2914,7 +2994,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B7" s="2">
         <v>46238</v>
       </c>
@@ -2958,7 +3038,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B8" s="2">
         <v>46239</v>
       </c>
@@ -3002,7 +3082,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="2:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:18" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B9" s="16">
         <v>46240</v>
       </c>
@@ -3046,7 +3126,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B10" s="2">
         <v>46241</v>
       </c>
@@ -3090,7 +3170,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B11" s="2">
         <v>46242</v>
       </c>
@@ -3134,7 +3214,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B12" s="2">
         <v>46243</v>
       </c>
@@ -3178,7 +3258,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B13" s="2">
         <v>46244</v>
       </c>
@@ -3222,7 +3302,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B14" s="2">
         <v>46245</v>
       </c>
@@ -3266,7 +3346,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="2:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:18" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B15" s="16">
         <v>46246</v>
       </c>
@@ -3310,7 +3390,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B16" s="2">
         <v>46247</v>
       </c>
@@ -3354,7 +3434,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B17" s="2">
         <v>46248</v>
       </c>
@@ -3398,7 +3478,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B18" s="2">
         <v>46249</v>
       </c>
@@ -3442,7 +3522,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B19" s="2">
         <v>46250</v>
       </c>
@@ -3486,7 +3566,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B20" s="2">
         <v>46251</v>
       </c>
@@ -3530,7 +3610,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="2:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B21" s="16">
         <v>46252</v>
       </c>
@@ -3574,7 +3654,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B22" s="2">
         <v>46253</v>
       </c>
@@ -3618,7 +3698,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B23" s="2">
         <v>46254</v>
       </c>
@@ -3662,7 +3742,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B24" s="2">
         <v>46255</v>
       </c>
@@ -3706,7 +3786,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B25" s="2">
         <v>46256</v>
       </c>
@@ -3750,7 +3830,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B26" s="2">
         <v>46257</v>
       </c>
@@ -3794,7 +3874,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="2:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B27" s="16">
         <v>46258</v>
       </c>
@@ -3838,7 +3918,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B28" s="2">
         <v>46259</v>
       </c>
@@ -3882,7 +3962,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B29" s="2">
         <v>46260</v>
       </c>
@@ -3926,7 +4006,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B30" s="2">
         <v>46261</v>
       </c>
@@ -3970,7 +4050,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B31" s="2">
         <v>46262</v>
       </c>
@@ -4014,7 +4094,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B32" s="2">
         <v>46263</v>
       </c>
@@ -4058,7 +4138,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="2:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B33" s="16">
         <v>46264</v>
       </c>
@@ -4102,7 +4182,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B34" s="2">
         <v>46265</v>
       </c>
@@ -4146,7 +4226,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.35">
       <c r="C39" s="15">
         <v>1</v>
       </c>
@@ -4179,7 +4259,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
       <c r="C40" s="15">
         <v>2</v>
       </c>
@@ -4212,7 +4292,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:15" x14ac:dyDescent="0.35">
       <c r="C41" s="15">
         <v>3</v>
       </c>
@@ -4245,7 +4325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.35">
       <c r="C42" s="15">
         <v>4</v>
       </c>
@@ -4278,7 +4358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.35">
       <c r="C43" s="15">
         <v>5</v>
       </c>
@@ -4311,7 +4391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.35">
       <c r="C44" s="15">
         <v>6</v>
       </c>
@@ -4344,7 +4424,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.35">
       <c r="C47" s="4">
         <v>0</v>
       </c>
@@ -4352,7 +4432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
       <c r="C48" s="4">
         <v>1</v>
       </c>
@@ -4360,7 +4440,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C49" s="4">
         <v>2</v>
       </c>
@@ -4368,7 +4448,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C50" s="4">
         <v>3</v>
       </c>
@@ -4376,7 +4456,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C52" s="4">
         <v>0</v>
       </c>
@@ -4387,17 +4467,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C53" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C54" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C55" s="4">
         <v>3</v>
       </c>
@@ -4445,4 +4525,1566 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C68A839-28BE-48F7-974A-BC1344349254}">
+  <dimension ref="B3:P39"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="3" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O3" t="s">
+        <v>50</v>
+      </c>
+      <c r="P3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J4" t="s">
+        <v>64</v>
+      </c>
+      <c r="K4" t="s">
+        <v>66</v>
+      </c>
+      <c r="L4" t="s">
+        <v>65</v>
+      </c>
+      <c r="M4" t="s">
+        <v>64</v>
+      </c>
+      <c r="N4" t="s">
+        <v>66</v>
+      </c>
+      <c r="O4" t="s">
+        <v>66</v>
+      </c>
+      <c r="P4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" t="s">
+        <v>36</v>
+      </c>
+      <c r="N5" t="s">
+        <v>37</v>
+      </c>
+      <c r="O5" t="s">
+        <v>38</v>
+      </c>
+      <c r="P5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K6" t="s">
+        <v>66</v>
+      </c>
+      <c r="L6" t="s">
+        <v>65</v>
+      </c>
+      <c r="M6" t="s">
+        <v>64</v>
+      </c>
+      <c r="N6" t="s">
+        <v>66</v>
+      </c>
+      <c r="O6" t="s">
+        <v>66</v>
+      </c>
+      <c r="P6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B7" s="18">
+        <v>46296</v>
+      </c>
+      <c r="C7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H7" t="s">
+        <v>73</v>
+      </c>
+      <c r="I7" t="s">
+        <v>74</v>
+      </c>
+      <c r="J7" t="s">
+        <v>75</v>
+      </c>
+      <c r="K7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L7" t="s">
+        <v>77</v>
+      </c>
+      <c r="M7" t="s">
+        <v>78</v>
+      </c>
+      <c r="N7" t="s">
+        <v>79</v>
+      </c>
+      <c r="O7" t="s">
+        <v>80</v>
+      </c>
+      <c r="P7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B8" s="18">
+        <v>46297</v>
+      </c>
+      <c r="C8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" t="s">
+        <v>81</v>
+      </c>
+      <c r="E8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F8" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I8" t="s">
+        <v>74</v>
+      </c>
+      <c r="J8" t="s">
+        <v>75</v>
+      </c>
+      <c r="K8" t="s">
+        <v>76</v>
+      </c>
+      <c r="L8" t="s">
+        <v>77</v>
+      </c>
+      <c r="M8" t="s">
+        <v>78</v>
+      </c>
+      <c r="N8" t="s">
+        <v>79</v>
+      </c>
+      <c r="O8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B9" s="18">
+        <v>46298</v>
+      </c>
+      <c r="C9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" t="s">
+        <v>81</v>
+      </c>
+      <c r="E9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I9" t="s">
+        <v>74</v>
+      </c>
+      <c r="J9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K9" t="s">
+        <v>79</v>
+      </c>
+      <c r="L9" t="s">
+        <v>80</v>
+      </c>
+      <c r="M9" t="s">
+        <v>75</v>
+      </c>
+      <c r="N9" t="s">
+        <v>76</v>
+      </c>
+      <c r="O9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B10" s="18">
+        <v>46299</v>
+      </c>
+      <c r="C10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" t="s">
+        <v>70</v>
+      </c>
+      <c r="F10" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" t="s">
+        <v>69</v>
+      </c>
+      <c r="H10" t="s">
+        <v>73</v>
+      </c>
+      <c r="I10" t="s">
+        <v>74</v>
+      </c>
+      <c r="J10" t="s">
+        <v>78</v>
+      </c>
+      <c r="K10" t="s">
+        <v>79</v>
+      </c>
+      <c r="L10" t="s">
+        <v>80</v>
+      </c>
+      <c r="M10" t="s">
+        <v>75</v>
+      </c>
+      <c r="N10" t="s">
+        <v>76</v>
+      </c>
+      <c r="O10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B11" s="18">
+        <v>46300</v>
+      </c>
+      <c r="C11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" t="s">
+        <v>75</v>
+      </c>
+      <c r="H11" t="s">
+        <v>76</v>
+      </c>
+      <c r="I11" t="s">
+        <v>77</v>
+      </c>
+      <c r="J11" t="s">
+        <v>78</v>
+      </c>
+      <c r="K11" t="s">
+        <v>79</v>
+      </c>
+      <c r="L11" t="s">
+        <v>80</v>
+      </c>
+      <c r="M11" t="s">
+        <v>69</v>
+      </c>
+      <c r="N11" t="s">
+        <v>73</v>
+      </c>
+      <c r="O11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B12" s="18">
+        <v>46301</v>
+      </c>
+      <c r="C12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" t="s">
+        <v>71</v>
+      </c>
+      <c r="G12" t="s">
+        <v>75</v>
+      </c>
+      <c r="H12" t="s">
+        <v>76</v>
+      </c>
+      <c r="I12" t="s">
+        <v>77</v>
+      </c>
+      <c r="J12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K12" t="s">
+        <v>79</v>
+      </c>
+      <c r="L12" t="s">
+        <v>80</v>
+      </c>
+      <c r="M12" t="s">
+        <v>69</v>
+      </c>
+      <c r="N12" t="s">
+        <v>73</v>
+      </c>
+      <c r="O12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B13" s="18">
+        <v>46302</v>
+      </c>
+      <c r="C13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" t="s">
+        <v>73</v>
+      </c>
+      <c r="F13" t="s">
+        <v>74</v>
+      </c>
+      <c r="G13" t="s">
+        <v>75</v>
+      </c>
+      <c r="H13" t="s">
+        <v>76</v>
+      </c>
+      <c r="I13" t="s">
+        <v>77</v>
+      </c>
+      <c r="J13" t="s">
+        <v>78</v>
+      </c>
+      <c r="K13" t="s">
+        <v>79</v>
+      </c>
+      <c r="L13" t="s">
+        <v>80</v>
+      </c>
+      <c r="M13" t="s">
+        <v>81</v>
+      </c>
+      <c r="N13" t="s">
+        <v>70</v>
+      </c>
+      <c r="O13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B14" s="18">
+        <v>46303</v>
+      </c>
+      <c r="C14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" t="s">
+        <v>73</v>
+      </c>
+      <c r="F14" t="s">
+        <v>74</v>
+      </c>
+      <c r="G14" t="s">
+        <v>75</v>
+      </c>
+      <c r="H14" t="s">
+        <v>76</v>
+      </c>
+      <c r="I14" t="s">
+        <v>77</v>
+      </c>
+      <c r="J14" t="s">
+        <v>78</v>
+      </c>
+      <c r="K14" t="s">
+        <v>79</v>
+      </c>
+      <c r="L14" t="s">
+        <v>80</v>
+      </c>
+      <c r="M14" t="s">
+        <v>81</v>
+      </c>
+      <c r="N14" t="s">
+        <v>70</v>
+      </c>
+      <c r="O14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B15" s="18">
+        <v>46304</v>
+      </c>
+      <c r="C15" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" t="s">
+        <v>73</v>
+      </c>
+      <c r="F15" t="s">
+        <v>74</v>
+      </c>
+      <c r="G15" t="s">
+        <v>75</v>
+      </c>
+      <c r="H15" t="s">
+        <v>76</v>
+      </c>
+      <c r="I15" t="s">
+        <v>77</v>
+      </c>
+      <c r="J15" t="s">
+        <v>81</v>
+      </c>
+      <c r="K15" t="s">
+        <v>70</v>
+      </c>
+      <c r="L15" t="s">
+        <v>71</v>
+      </c>
+      <c r="M15" t="s">
+        <v>78</v>
+      </c>
+      <c r="N15" t="s">
+        <v>79</v>
+      </c>
+      <c r="O15" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B16" s="18">
+        <v>46305</v>
+      </c>
+      <c r="C16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16" t="s">
+        <v>74</v>
+      </c>
+      <c r="G16" t="s">
+        <v>75</v>
+      </c>
+      <c r="H16" t="s">
+        <v>82</v>
+      </c>
+      <c r="I16" t="s">
+        <v>77</v>
+      </c>
+      <c r="J16" t="s">
+        <v>81</v>
+      </c>
+      <c r="K16" t="s">
+        <v>70</v>
+      </c>
+      <c r="L16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N16" t="s">
+        <v>79</v>
+      </c>
+      <c r="O16" t="s">
+        <v>80</v>
+      </c>
+      <c r="P16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B17" s="18">
+        <v>46306</v>
+      </c>
+      <c r="C17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" t="s">
+        <v>73</v>
+      </c>
+      <c r="F17" t="s">
+        <v>74</v>
+      </c>
+      <c r="G17" t="s">
+        <v>78</v>
+      </c>
+      <c r="H17" t="s">
+        <v>79</v>
+      </c>
+      <c r="I17" t="s">
+        <v>80</v>
+      </c>
+      <c r="J17" t="s">
+        <v>81</v>
+      </c>
+      <c r="K17" t="s">
+        <v>70</v>
+      </c>
+      <c r="L17" t="s">
+        <v>71</v>
+      </c>
+      <c r="M17" t="s">
+        <v>75</v>
+      </c>
+      <c r="N17" t="s">
+        <v>76</v>
+      </c>
+      <c r="O17" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B18" s="18">
+        <v>46307</v>
+      </c>
+      <c r="C18" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" t="s">
+        <v>73</v>
+      </c>
+      <c r="F18" t="s">
+        <v>74</v>
+      </c>
+      <c r="G18" t="s">
+        <v>78</v>
+      </c>
+      <c r="H18" t="s">
+        <v>79</v>
+      </c>
+      <c r="I18" t="s">
+        <v>80</v>
+      </c>
+      <c r="J18" t="s">
+        <v>81</v>
+      </c>
+      <c r="K18" t="s">
+        <v>70</v>
+      </c>
+      <c r="L18" t="s">
+        <v>71</v>
+      </c>
+      <c r="M18" t="s">
+        <v>75</v>
+      </c>
+      <c r="N18" t="s">
+        <v>76</v>
+      </c>
+      <c r="O18" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B19" s="18">
+        <v>46308</v>
+      </c>
+      <c r="C19" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F19" t="s">
+        <v>77</v>
+      </c>
+      <c r="G19" t="s">
+        <v>78</v>
+      </c>
+      <c r="H19" t="s">
+        <v>79</v>
+      </c>
+      <c r="I19" t="s">
+        <v>80</v>
+      </c>
+      <c r="J19" t="s">
+        <v>81</v>
+      </c>
+      <c r="K19" t="s">
+        <v>70</v>
+      </c>
+      <c r="L19" t="s">
+        <v>71</v>
+      </c>
+      <c r="M19" t="s">
+        <v>69</v>
+      </c>
+      <c r="N19" t="s">
+        <v>73</v>
+      </c>
+      <c r="O19" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B20" s="18">
+        <v>46309</v>
+      </c>
+      <c r="C20" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" t="s">
+        <v>76</v>
+      </c>
+      <c r="F20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G20" t="s">
+        <v>78</v>
+      </c>
+      <c r="H20" t="s">
+        <v>79</v>
+      </c>
+      <c r="I20" t="s">
+        <v>80</v>
+      </c>
+      <c r="J20" t="s">
+        <v>81</v>
+      </c>
+      <c r="K20" t="s">
+        <v>70</v>
+      </c>
+      <c r="L20" t="s">
+        <v>71</v>
+      </c>
+      <c r="M20" t="s">
+        <v>69</v>
+      </c>
+      <c r="N20" t="s">
+        <v>73</v>
+      </c>
+      <c r="O20" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B21" s="18">
+        <v>46310</v>
+      </c>
+      <c r="C21" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" t="s">
+        <v>76</v>
+      </c>
+      <c r="F21" t="s">
+        <v>77</v>
+      </c>
+      <c r="G21" t="s">
+        <v>78</v>
+      </c>
+      <c r="H21" t="s">
+        <v>79</v>
+      </c>
+      <c r="I21" t="s">
+        <v>80</v>
+      </c>
+      <c r="J21" t="s">
+        <v>69</v>
+      </c>
+      <c r="K21" t="s">
+        <v>73</v>
+      </c>
+      <c r="L21" t="s">
+        <v>74</v>
+      </c>
+      <c r="M21" t="s">
+        <v>81</v>
+      </c>
+      <c r="N21" t="s">
+        <v>70</v>
+      </c>
+      <c r="O21" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B22" s="18">
+        <v>46311</v>
+      </c>
+      <c r="C22" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" t="s">
+        <v>76</v>
+      </c>
+      <c r="F22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G22" t="s">
+        <v>78</v>
+      </c>
+      <c r="H22" t="s">
+        <v>79</v>
+      </c>
+      <c r="I22" t="s">
+        <v>80</v>
+      </c>
+      <c r="J22" t="s">
+        <v>69</v>
+      </c>
+      <c r="K22" t="s">
+        <v>73</v>
+      </c>
+      <c r="L22" t="s">
+        <v>74</v>
+      </c>
+      <c r="M22" t="s">
+        <v>81</v>
+      </c>
+      <c r="N22" t="s">
+        <v>70</v>
+      </c>
+      <c r="O22" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B23" s="18">
+        <v>46312</v>
+      </c>
+      <c r="C23" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" t="s">
+        <v>75</v>
+      </c>
+      <c r="E23" t="s">
+        <v>76</v>
+      </c>
+      <c r="F23" t="s">
+        <v>77</v>
+      </c>
+      <c r="G23" t="s">
+        <v>81</v>
+      </c>
+      <c r="H23" t="s">
+        <v>70</v>
+      </c>
+      <c r="I23" t="s">
+        <v>71</v>
+      </c>
+      <c r="J23" t="s">
+        <v>69</v>
+      </c>
+      <c r="K23" t="s">
+        <v>73</v>
+      </c>
+      <c r="L23" t="s">
+        <v>74</v>
+      </c>
+      <c r="M23" t="s">
+        <v>78</v>
+      </c>
+      <c r="N23" t="s">
+        <v>79</v>
+      </c>
+      <c r="O23" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B24" s="18">
+        <v>46313</v>
+      </c>
+      <c r="C24" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" t="s">
+        <v>75</v>
+      </c>
+      <c r="E24" t="s">
+        <v>76</v>
+      </c>
+      <c r="F24" t="s">
+        <v>77</v>
+      </c>
+      <c r="G24" t="s">
+        <v>81</v>
+      </c>
+      <c r="H24" t="s">
+        <v>70</v>
+      </c>
+      <c r="I24" t="s">
+        <v>71</v>
+      </c>
+      <c r="J24" t="s">
+        <v>69</v>
+      </c>
+      <c r="K24" t="s">
+        <v>73</v>
+      </c>
+      <c r="L24" t="s">
+        <v>74</v>
+      </c>
+      <c r="M24" t="s">
+        <v>78</v>
+      </c>
+      <c r="N24" t="s">
+        <v>79</v>
+      </c>
+      <c r="O24" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B25" s="18">
+        <v>46314</v>
+      </c>
+      <c r="C25" t="s">
+        <v>45</v>
+      </c>
+      <c r="D25" t="s">
+        <v>78</v>
+      </c>
+      <c r="E25" t="s">
+        <v>79</v>
+      </c>
+      <c r="F25" t="s">
+        <v>80</v>
+      </c>
+      <c r="G25" t="s">
+        <v>81</v>
+      </c>
+      <c r="H25" t="s">
+        <v>70</v>
+      </c>
+      <c r="I25" t="s">
+        <v>71</v>
+      </c>
+      <c r="J25" t="s">
+        <v>69</v>
+      </c>
+      <c r="K25" t="s">
+        <v>73</v>
+      </c>
+      <c r="L25" t="s">
+        <v>74</v>
+      </c>
+      <c r="M25" t="s">
+        <v>75</v>
+      </c>
+      <c r="N25" t="s">
+        <v>76</v>
+      </c>
+      <c r="O25" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B26" s="18">
+        <v>46315</v>
+      </c>
+      <c r="C26" t="s">
+        <v>46</v>
+      </c>
+      <c r="D26" t="s">
+        <v>78</v>
+      </c>
+      <c r="E26" t="s">
+        <v>79</v>
+      </c>
+      <c r="F26" t="s">
+        <v>71</v>
+      </c>
+      <c r="G26" t="s">
+        <v>81</v>
+      </c>
+      <c r="H26" t="s">
+        <v>70</v>
+      </c>
+      <c r="I26" t="s">
+        <v>83</v>
+      </c>
+      <c r="J26" t="s">
+        <v>69</v>
+      </c>
+      <c r="K26" t="s">
+        <v>73</v>
+      </c>
+      <c r="L26" t="s">
+        <v>74</v>
+      </c>
+      <c r="M26" t="s">
+        <v>75</v>
+      </c>
+      <c r="N26" t="s">
+        <v>76</v>
+      </c>
+      <c r="O26" t="s">
+        <v>77</v>
+      </c>
+      <c r="P26" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B27" s="18">
+        <v>46316</v>
+      </c>
+      <c r="C27" t="s">
+        <v>47</v>
+      </c>
+      <c r="D27" t="s">
+        <v>78</v>
+      </c>
+      <c r="E27" t="s">
+        <v>79</v>
+      </c>
+      <c r="F27" t="s">
+        <v>80</v>
+      </c>
+      <c r="G27" t="s">
+        <v>81</v>
+      </c>
+      <c r="H27" t="s">
+        <v>70</v>
+      </c>
+      <c r="I27" t="s">
+        <v>71</v>
+      </c>
+      <c r="J27" t="s">
+        <v>75</v>
+      </c>
+      <c r="K27" t="s">
+        <v>76</v>
+      </c>
+      <c r="L27" t="s">
+        <v>77</v>
+      </c>
+      <c r="M27" t="s">
+        <v>69</v>
+      </c>
+      <c r="N27" t="s">
+        <v>73</v>
+      </c>
+      <c r="O27" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B28" s="18">
+        <v>46317</v>
+      </c>
+      <c r="C28" t="s">
+        <v>48</v>
+      </c>
+      <c r="D28" t="s">
+        <v>78</v>
+      </c>
+      <c r="E28" t="s">
+        <v>79</v>
+      </c>
+      <c r="F28" t="s">
+        <v>80</v>
+      </c>
+      <c r="G28" t="s">
+        <v>81</v>
+      </c>
+      <c r="H28" t="s">
+        <v>70</v>
+      </c>
+      <c r="I28" t="s">
+        <v>71</v>
+      </c>
+      <c r="J28" t="s">
+        <v>75</v>
+      </c>
+      <c r="K28" t="s">
+        <v>76</v>
+      </c>
+      <c r="L28" t="s">
+        <v>77</v>
+      </c>
+      <c r="M28" t="s">
+        <v>69</v>
+      </c>
+      <c r="N28" t="s">
+        <v>73</v>
+      </c>
+      <c r="O28" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B29" s="18">
+        <v>46318</v>
+      </c>
+      <c r="C29" t="s">
+        <v>49</v>
+      </c>
+      <c r="D29" t="s">
+        <v>78</v>
+      </c>
+      <c r="E29" t="s">
+        <v>79</v>
+      </c>
+      <c r="F29" t="s">
+        <v>80</v>
+      </c>
+      <c r="G29" t="s">
+        <v>69</v>
+      </c>
+      <c r="H29" t="s">
+        <v>73</v>
+      </c>
+      <c r="I29" t="s">
+        <v>74</v>
+      </c>
+      <c r="J29" t="s">
+        <v>75</v>
+      </c>
+      <c r="K29" t="s">
+        <v>76</v>
+      </c>
+      <c r="L29" t="s">
+        <v>77</v>
+      </c>
+      <c r="M29" t="s">
+        <v>81</v>
+      </c>
+      <c r="N29" t="s">
+        <v>70</v>
+      </c>
+      <c r="O29" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B30" s="18">
+        <v>46319</v>
+      </c>
+      <c r="C30" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" t="s">
+        <v>78</v>
+      </c>
+      <c r="E30" t="s">
+        <v>79</v>
+      </c>
+      <c r="F30" t="s">
+        <v>80</v>
+      </c>
+      <c r="G30" t="s">
+        <v>69</v>
+      </c>
+      <c r="H30" t="s">
+        <v>73</v>
+      </c>
+      <c r="I30" t="s">
+        <v>74</v>
+      </c>
+      <c r="J30" t="s">
+        <v>75</v>
+      </c>
+      <c r="K30" t="s">
+        <v>76</v>
+      </c>
+      <c r="L30" t="s">
+        <v>77</v>
+      </c>
+      <c r="M30" t="s">
+        <v>81</v>
+      </c>
+      <c r="N30" t="s">
+        <v>70</v>
+      </c>
+      <c r="O30" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B31" s="18">
+        <v>46320</v>
+      </c>
+      <c r="C31" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31" t="s">
+        <v>81</v>
+      </c>
+      <c r="E31" t="s">
+        <v>70</v>
+      </c>
+      <c r="F31" t="s">
+        <v>71</v>
+      </c>
+      <c r="G31" t="s">
+        <v>69</v>
+      </c>
+      <c r="H31" t="s">
+        <v>73</v>
+      </c>
+      <c r="I31" t="s">
+        <v>74</v>
+      </c>
+      <c r="J31" t="s">
+        <v>75</v>
+      </c>
+      <c r="K31" t="s">
+        <v>76</v>
+      </c>
+      <c r="L31" t="s">
+        <v>77</v>
+      </c>
+      <c r="M31" t="s">
+        <v>78</v>
+      </c>
+      <c r="N31" t="s">
+        <v>79</v>
+      </c>
+      <c r="O31" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B32" s="18">
+        <v>46321</v>
+      </c>
+      <c r="C32" t="s">
+        <v>45</v>
+      </c>
+      <c r="D32" t="s">
+        <v>81</v>
+      </c>
+      <c r="E32" t="s">
+        <v>70</v>
+      </c>
+      <c r="F32" t="s">
+        <v>71</v>
+      </c>
+      <c r="G32" t="s">
+        <v>69</v>
+      </c>
+      <c r="H32" t="s">
+        <v>73</v>
+      </c>
+      <c r="I32" t="s">
+        <v>74</v>
+      </c>
+      <c r="J32" t="s">
+        <v>75</v>
+      </c>
+      <c r="K32" t="s">
+        <v>76</v>
+      </c>
+      <c r="L32" t="s">
+        <v>77</v>
+      </c>
+      <c r="M32" t="s">
+        <v>78</v>
+      </c>
+      <c r="N32" t="s">
+        <v>79</v>
+      </c>
+      <c r="O32" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B33" s="18">
+        <v>46322</v>
+      </c>
+      <c r="C33" t="s">
+        <v>46</v>
+      </c>
+      <c r="D33" t="s">
+        <v>81</v>
+      </c>
+      <c r="E33" t="s">
+        <v>70</v>
+      </c>
+      <c r="F33" t="s">
+        <v>71</v>
+      </c>
+      <c r="G33" t="s">
+        <v>69</v>
+      </c>
+      <c r="H33" t="s">
+        <v>73</v>
+      </c>
+      <c r="I33" t="s">
+        <v>74</v>
+      </c>
+      <c r="J33" t="s">
+        <v>78</v>
+      </c>
+      <c r="K33" t="s">
+        <v>79</v>
+      </c>
+      <c r="L33" t="s">
+        <v>80</v>
+      </c>
+      <c r="M33" t="s">
+        <v>75</v>
+      </c>
+      <c r="N33" t="s">
+        <v>76</v>
+      </c>
+      <c r="O33" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B34" s="18">
+        <v>46323</v>
+      </c>
+      <c r="C34" t="s">
+        <v>47</v>
+      </c>
+      <c r="D34" t="s">
+        <v>81</v>
+      </c>
+      <c r="E34" t="s">
+        <v>70</v>
+      </c>
+      <c r="F34" t="s">
+        <v>71</v>
+      </c>
+      <c r="G34" t="s">
+        <v>69</v>
+      </c>
+      <c r="H34" t="s">
+        <v>73</v>
+      </c>
+      <c r="I34" t="s">
+        <v>74</v>
+      </c>
+      <c r="J34" t="s">
+        <v>78</v>
+      </c>
+      <c r="K34" t="s">
+        <v>79</v>
+      </c>
+      <c r="L34" t="s">
+        <v>80</v>
+      </c>
+      <c r="M34" t="s">
+        <v>75</v>
+      </c>
+      <c r="N34" t="s">
+        <v>76</v>
+      </c>
+      <c r="O34" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B35" s="18">
+        <v>46324</v>
+      </c>
+      <c r="C35" t="s">
+        <v>48</v>
+      </c>
+      <c r="D35" t="s">
+        <v>81</v>
+      </c>
+      <c r="E35" t="s">
+        <v>70</v>
+      </c>
+      <c r="F35" t="s">
+        <v>71</v>
+      </c>
+      <c r="G35" t="s">
+        <v>75</v>
+      </c>
+      <c r="H35" t="s">
+        <v>76</v>
+      </c>
+      <c r="I35" t="s">
+        <v>77</v>
+      </c>
+      <c r="J35" t="s">
+        <v>78</v>
+      </c>
+      <c r="K35" t="s">
+        <v>79</v>
+      </c>
+      <c r="L35" t="s">
+        <v>80</v>
+      </c>
+      <c r="M35" t="s">
+        <v>69</v>
+      </c>
+      <c r="N35" t="s">
+        <v>73</v>
+      </c>
+      <c r="O35" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B36" s="18">
+        <v>46325</v>
+      </c>
+      <c r="C36" t="s">
+        <v>49</v>
+      </c>
+      <c r="D36" t="s">
+        <v>81</v>
+      </c>
+      <c r="E36" t="s">
+        <v>70</v>
+      </c>
+      <c r="F36" t="s">
+        <v>71</v>
+      </c>
+      <c r="G36" t="s">
+        <v>75</v>
+      </c>
+      <c r="H36" t="s">
+        <v>76</v>
+      </c>
+      <c r="I36" t="s">
+        <v>77</v>
+      </c>
+      <c r="J36" t="s">
+        <v>78</v>
+      </c>
+      <c r="K36" t="s">
+        <v>79</v>
+      </c>
+      <c r="L36" t="s">
+        <v>80</v>
+      </c>
+      <c r="M36" t="s">
+        <v>69</v>
+      </c>
+      <c r="N36" t="s">
+        <v>73</v>
+      </c>
+      <c r="O36" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B37" s="18">
+        <v>46326</v>
+      </c>
+      <c r="C37" t="s">
+        <v>39</v>
+      </c>
+      <c r="D37" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" t="s">
+        <v>73</v>
+      </c>
+      <c r="F37" t="s">
+        <v>74</v>
+      </c>
+      <c r="G37" t="s">
+        <v>75</v>
+      </c>
+      <c r="H37" t="s">
+        <v>76</v>
+      </c>
+      <c r="I37" t="s">
+        <v>77</v>
+      </c>
+      <c r="J37" t="s">
+        <v>78</v>
+      </c>
+      <c r="K37" t="s">
+        <v>79</v>
+      </c>
+      <c r="L37" t="s">
+        <v>80</v>
+      </c>
+      <c r="M37" t="s">
+        <v>81</v>
+      </c>
+      <c r="N37" t="s">
+        <v>70</v>
+      </c>
+      <c r="O37" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="D39">
+        <v>11</v>
+      </c>
+      <c r="G39">
+        <v>6</v>
+      </c>
+      <c r="J39">
+        <v>6</v>
+      </c>
+      <c r="L39" s="19">
+        <f>D39+G39+J39</f>
+        <v>23</v>
+      </c>
+      <c r="M39">
+        <f>L39*8</f>
+        <v>184</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>